--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ycc/Desktop/Mcqueen_yang/高中/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A8BA6F2-0F33-5345-A9DB-301BC5D8837C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA7A5F8-670D-2B47-8A80-E9D1FEBCECC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{380A9301-B8AB-9742-828D-4D76A95B3924}"/>
   </bookViews>
@@ -36,60 +36,225 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="48">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">物理 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>周二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周五</t>
-  </si>
-  <si>
-    <t>课程1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>课程2</t>
-  </si>
-  <si>
-    <t>课程3</t>
-  </si>
-  <si>
-    <t>课程4</t>
-  </si>
-  <si>
-    <t>课程5</t>
-  </si>
-  <si>
-    <t>课程6</t>
-  </si>
-  <si>
-    <t>课程7</t>
-  </si>
-  <si>
-    <t>课程8</t>
-  </si>
-  <si>
-    <t>课程9</t>
-  </si>
-  <si>
-    <t>课程10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数学早读 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">体育 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">语文 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">化学 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数学 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">信息 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">生物 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">英语 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">班会 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语早读</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文早读</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:35-11:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7:00-7:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8:00-8:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8:50-9:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9:40-10:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:25-12:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:35-14:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:30-15:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:25-16:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:15-16:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18:00-19:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">语文早读 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">英语早读 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">历史 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">心理 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">艺术 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">选修 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">地理 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">强基 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">体育专项 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">政治 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">社团 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>紫竹讲坛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="SegoeUI"/>
+      </rPr>
+      <t>\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="SimSun"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">习读 </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">英语限时 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">物化限时 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">语文限时 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数学限时 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:00-13:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:55-14:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:50-15:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -104,6 +269,25 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SegoeUI"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,8 +312,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,195 +653,368 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3D7239-A928-7446-9C44-5E672C71E8B3}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="D14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -9,18 +9,17 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="等线"/>
       <charset val="134"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
@@ -28,23 +27,7 @@
     <font>
       <name val="等线"/>
       <charset val="134"/>
-      <family val="2"/>
       <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -74,9 +57,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -196,7 +177,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -229,26 +210,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -281,23 +245,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -460,11 +407,6 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -476,6 +418,9 @@
   </sheetPr>
   <dimension ref="A1:J400"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.8203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.17578125" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -483,331 +428,356 @@
           <t>周一</t>
         </is>
       </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="C1" s="0" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="G1" s="0" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I1" s="0" t="inlineStr">
         <is>
           <t>周五</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学早读 </t>
+          <t>课程</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文早读 </t>
+          <t>课程</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>英语早读</t>
+          <t>课程</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
-          <t>语文早读</t>
+          <t>课程</t>
         </is>
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">英语早读 </t>
+          <t>课程</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理 </t>
+          <t xml:space="preserve">数学早读 </t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t xml:space="preserve">语文早读 </t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理 </t>
+          <t>英语早读</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>数学</t>
+          <t>语文早读</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">英语 </t>
+          <t xml:space="preserve">英语早读 </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>8:50-9:30</t>
+          <t>8:00-8:40</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">体育 </t>
+          <t xml:space="preserve">物理 </t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>8:50-9:30</t>
+          <t>8:00-8:40</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">历史 </t>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>8:50-9:30</t>
+          <t>8:00-8:40</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">英语 </t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>8:50-9:30</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">数学 </t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t>8:50-9:30</t>
-        </is>
-      </c>
-      <c r="J4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">体育 </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t xml:space="preserve">体育 </t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">历史 </t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">英语 </t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>9:40-10:20</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">历史 </t>
-        </is>
-      </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t xml:space="preserve">数学 </t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">生物 </t>
+          <t xml:space="preserve">体育 </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">化学 </t>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">心理 </t>
+          <t xml:space="preserve">英语 </t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">艺术 </t>
+          <t xml:space="preserve">历史 </t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">信息 </t>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">选修 </t>
+          <t xml:space="preserve">生物 </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学 </t>
+          <t xml:space="preserve">化学 </t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">地理 </t>
+          <t xml:space="preserve">心理 </t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学 </t>
+          <t xml:space="preserve">艺术 </t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">化学 </t>
+          <t xml:space="preserve">信息 </t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -819,318 +789,617 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>13:35-14:15</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">信息 </t>
+          <t xml:space="preserve">数学 </t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>13:35-14:15</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">地理 </t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">数学 </t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>13:35-14:15</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">语文 </t>
-        </is>
-      </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>13:35-14:15</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">英语 </t>
+          <t xml:space="preserve">化学 </t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t>13:00-13:40</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学 </t>
+          <t xml:space="preserve">选修 </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">生物 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">化学 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">地理 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">强基 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>13:55-14:35</t>
+          <t>12:40-13:00</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t>午休</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>15:25-16:05</t>
+          <t>13:35-14:15</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">信息 </t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">英语 </t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>15:25-16:05</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">体育专项 </t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>15:25-16:05</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">政治 </t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>15:25-16:05</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">物理 </t>
-        </is>
-      </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>14:50-15:30</t>
+          <t>13:00-13:40</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">政治 </t>
+          <t xml:space="preserve">数学 </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">班会 </t>
+          <t xml:space="preserve">生物 </t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">体育专项 </t>
+          <t xml:space="preserve">化学 </t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">社团 </t>
+          <t xml:space="preserve">地理 </t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>紫竹讲坛\习读</t>
+          <t xml:space="preserve">强基 </t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>13:55-14:35</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育专项 </t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">政治 </t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>14:50-15:30</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">政治 </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">班会 </t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育专项 </t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">社团 </t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>紫竹讲坛\习读</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">英语限时 </t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">物化限时 </t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">语文限时 </t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">数学限时 </t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="D14" s="1" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>程子曦</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>康立轩</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>陈奕浩</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>倪宥霖</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>叶宇乐</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>孙丞怿</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>黄思源</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>李玥呈</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>张一铭</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>沈俊奕</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>font_size</t>
         </is>
       </c>
-      <c r="B20" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="B30" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>window_width</t>
         </is>
       </c>
-      <c r="B21" s="0" t="n">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
+      <c r="B31" s="0" t="n">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>window_height</t>
         </is>
       </c>
-      <c r="B22" s="0" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="B32" s="0" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>excel_path</t>
         </is>
       </c>
-      <c r="B23" s="0" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>D:\tools\ClassroomListener\schedule.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>col_width_0</t>
         </is>
       </c>
-      <c r="B24" s="0" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
+      <c r="B34" s="0" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>col_width_1</t>
         </is>
       </c>
-      <c r="B25" s="0" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
+      <c r="B35" s="0" t="n">
+        <v>190</v>
+      </c>
+    </row>
     <row r="36"/>
     <row r="37"/>
     <row r="38"/>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -28,6 +28,14 @@
       <name val="等线"/>
       <charset val="134"/>
       <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,11 +61,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -416,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J400"/>
+  <dimension ref="A1:AB400"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.8203125" defaultRowHeight="15"/>
   <cols>
     <col width="12.17578125" customWidth="1" style="1" min="8" max="8"/>
@@ -473,6 +484,76 @@
           <t>/</t>
         </is>
       </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O1" s="0" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="R1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="S1" s="0" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="T1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="U1" s="0" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="V1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="W1" s="0" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="X1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AA1" s="0" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="AB1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -525,6 +606,76 @@
           <t>课程</t>
         </is>
       </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="S2" s="0" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="T2" s="0" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="U2" s="0" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="V2" s="0" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="W2" s="0" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="X2" s="0" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="AA2" s="0" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="AB2" s="0" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -577,6 +728,76 @@
           <t xml:space="preserve">英语早读 </t>
         </is>
       </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>7:00-7:30</t>
+        </is>
+      </c>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学早读 </t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>7:00-7:30</t>
+        </is>
+      </c>
+      <c r="P3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学早读 </t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>7:00-7:30</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文早读 </t>
+        </is>
+      </c>
+      <c r="S3" s="0" t="inlineStr">
+        <is>
+          <t>7:00-7:30</t>
+        </is>
+      </c>
+      <c r="T3" s="0" t="inlineStr">
+        <is>
+          <t>英语早读</t>
+        </is>
+      </c>
+      <c r="U3" s="0" t="inlineStr">
+        <is>
+          <t>7:00-7:30</t>
+        </is>
+      </c>
+      <c r="V3" s="0" t="inlineStr">
+        <is>
+          <t>语文早读</t>
+        </is>
+      </c>
+      <c r="W3" s="0" t="inlineStr">
+        <is>
+          <t>7:00-7:30</t>
+        </is>
+      </c>
+      <c r="X3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语早读 </t>
+        </is>
+      </c>
+      <c r="AA3" s="0" t="inlineStr">
+        <is>
+          <t>7:00-7:30</t>
+        </is>
+      </c>
+      <c r="AB3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学早读 </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -629,6 +850,76 @@
           <t xml:space="preserve">英语 </t>
         </is>
       </c>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="P4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="Q4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="S4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="T4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="U4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="V4" s="0" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="W4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="X4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="AA4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="AB4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -681,6 +972,76 @@
           <t xml:space="preserve">体育 </t>
         </is>
       </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育 </t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="P5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育 </t>
+        </is>
+      </c>
+      <c r="Q5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="R5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">历史 </t>
+        </is>
+      </c>
+      <c r="S5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="T5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="U5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="V5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="W5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="X5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育 </t>
+        </is>
+      </c>
+      <c r="AA5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="AB5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育 </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -733,6 +1094,76 @@
           <t xml:space="preserve">生物 </t>
         </is>
       </c>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>9:40-10:20</t>
+        </is>
+      </c>
+      <c r="N6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="O6" s="0" t="inlineStr">
+        <is>
+          <t>9:40-10:20</t>
+        </is>
+      </c>
+      <c r="P6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="Q6" s="0" t="inlineStr">
+        <is>
+          <t>9:40-10:20</t>
+        </is>
+      </c>
+      <c r="R6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="S6" s="0" t="inlineStr">
+        <is>
+          <t>9:40-10:20</t>
+        </is>
+      </c>
+      <c r="T6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">历史 </t>
+        </is>
+      </c>
+      <c r="U6" s="0" t="inlineStr">
+        <is>
+          <t>9:40-10:20</t>
+        </is>
+      </c>
+      <c r="V6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="W6" s="0" t="inlineStr">
+        <is>
+          <t>9:40-10:20</t>
+        </is>
+      </c>
+      <c r="X6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生物 </t>
+        </is>
+      </c>
+      <c r="AA6" s="0" t="inlineStr">
+        <is>
+          <t>9:40-10:20</t>
+        </is>
+      </c>
+      <c r="AB6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -785,6 +1216,76 @@
           <t xml:space="preserve">选修 </t>
         </is>
       </c>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>10:35-11:15</t>
+        </is>
+      </c>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">化学 </t>
+        </is>
+      </c>
+      <c r="O7" s="0" t="inlineStr">
+        <is>
+          <t>10:35-11:15</t>
+        </is>
+      </c>
+      <c r="P7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">化学 </t>
+        </is>
+      </c>
+      <c r="Q7" s="0" t="inlineStr">
+        <is>
+          <t>10:35-11:15</t>
+        </is>
+      </c>
+      <c r="R7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">心理 </t>
+        </is>
+      </c>
+      <c r="S7" s="0" t="inlineStr">
+        <is>
+          <t>10:35-11:15</t>
+        </is>
+      </c>
+      <c r="T7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">艺术 </t>
+        </is>
+      </c>
+      <c r="U7" s="0" t="inlineStr">
+        <is>
+          <t>10:35-11:15</t>
+        </is>
+      </c>
+      <c r="V7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">信息 </t>
+        </is>
+      </c>
+      <c r="W7" s="0" t="inlineStr">
+        <is>
+          <t>10:35-11:15</t>
+        </is>
+      </c>
+      <c r="X7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">选修 </t>
+        </is>
+      </c>
+      <c r="AA7" s="0" t="inlineStr">
+        <is>
+          <t>10:35-11:15</t>
+        </is>
+      </c>
+      <c r="AB7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">化学 </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -837,6 +1338,76 @@
           <t xml:space="preserve">选修 </t>
         </is>
       </c>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="N8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="Q8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="R8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地理 </t>
+        </is>
+      </c>
+      <c r="S8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="T8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="U8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="V8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">化学 </t>
+        </is>
+      </c>
+      <c r="W8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="X8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">选修 </t>
+        </is>
+      </c>
+      <c r="AA8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="AB8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -889,6 +1460,76 @@
           <t>午休</t>
         </is>
       </c>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t>13:10-13:30</t>
+        </is>
+      </c>
+      <c r="N9" s="0" t="inlineStr">
+        <is>
+          <t>午休</t>
+        </is>
+      </c>
+      <c r="O9" s="0" t="inlineStr">
+        <is>
+          <t>13:10-13:30</t>
+        </is>
+      </c>
+      <c r="P9" s="0" t="inlineStr">
+        <is>
+          <t>午休</t>
+        </is>
+      </c>
+      <c r="Q9" s="0" t="inlineStr">
+        <is>
+          <t>13:10-13:30</t>
+        </is>
+      </c>
+      <c r="R9" s="0" t="inlineStr">
+        <is>
+          <t>午休</t>
+        </is>
+      </c>
+      <c r="S9" s="0" t="inlineStr">
+        <is>
+          <t>13:10-13:30</t>
+        </is>
+      </c>
+      <c r="T9" s="0" t="inlineStr">
+        <is>
+          <t>午休</t>
+        </is>
+      </c>
+      <c r="U9" s="0" t="inlineStr">
+        <is>
+          <t>13:10-13:30</t>
+        </is>
+      </c>
+      <c r="V9" s="0" t="inlineStr">
+        <is>
+          <t>午休</t>
+        </is>
+      </c>
+      <c r="W9" s="0" t="inlineStr">
+        <is>
+          <t>12:40-13:00</t>
+        </is>
+      </c>
+      <c r="X9" s="0" t="inlineStr">
+        <is>
+          <t>午休</t>
+        </is>
+      </c>
+      <c r="AA9" s="0" t="inlineStr">
+        <is>
+          <t>13:10-13:30</t>
+        </is>
+      </c>
+      <c r="AB9" s="0" t="inlineStr">
+        <is>
+          <t>午休</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -941,6 +1582,76 @@
           <t xml:space="preserve">数学 </t>
         </is>
       </c>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="N10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">信息 </t>
+        </is>
+      </c>
+      <c r="O10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">信息 </t>
+        </is>
+      </c>
+      <c r="Q10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="R10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="S10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="T10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="U10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="V10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="W10" s="0" t="inlineStr">
+        <is>
+          <t>13:00-13:40</t>
+        </is>
+      </c>
+      <c r="X10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="AA10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="AB10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">信息 </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
@@ -993,6 +1704,76 @@
           <t xml:space="preserve">语文 </t>
         </is>
       </c>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>14:30-15:10</t>
+        </is>
+      </c>
+      <c r="N11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生物 </t>
+        </is>
+      </c>
+      <c r="O11" s="0" t="inlineStr">
+        <is>
+          <t>14:30-15:10</t>
+        </is>
+      </c>
+      <c r="P11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生物 </t>
+        </is>
+      </c>
+      <c r="Q11" s="0" t="inlineStr">
+        <is>
+          <t>14:30-15:10</t>
+        </is>
+      </c>
+      <c r="R11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">化学 </t>
+        </is>
+      </c>
+      <c r="S11" s="0" t="inlineStr">
+        <is>
+          <t>14:30-15:10</t>
+        </is>
+      </c>
+      <c r="T11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地理 </t>
+        </is>
+      </c>
+      <c r="U11" s="0" t="inlineStr">
+        <is>
+          <t>14:30-15:10</t>
+        </is>
+      </c>
+      <c r="V11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">强基 </t>
+        </is>
+      </c>
+      <c r="W11" s="0" t="inlineStr">
+        <is>
+          <t>13:55-14:35</t>
+        </is>
+      </c>
+      <c r="X11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="AA11" s="0" t="inlineStr">
+        <is>
+          <t>14:30-15:10</t>
+        </is>
+      </c>
+      <c r="AB11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生物 </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -1045,6 +1826,76 @@
           <t xml:space="preserve">政治 </t>
         </is>
       </c>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="N12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="O12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="P12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="Q12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="R12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育专项 </t>
+        </is>
+      </c>
+      <c r="S12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="T12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">政治 </t>
+        </is>
+      </c>
+      <c r="U12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="V12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="W12" s="0" t="inlineStr">
+        <is>
+          <t>14:50-15:30</t>
+        </is>
+      </c>
+      <c r="X12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">政治 </t>
+        </is>
+      </c>
+      <c r="AA12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="AB12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -1097,6 +1948,76 @@
           <t>END_C</t>
         </is>
       </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="N13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">班会 </t>
+        </is>
+      </c>
+      <c r="O13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="P13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">班会 </t>
+        </is>
+      </c>
+      <c r="Q13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="R13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育专项 </t>
+        </is>
+      </c>
+      <c r="S13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="T13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">社团 </t>
+        </is>
+      </c>
+      <c r="U13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="V13" s="0" t="inlineStr">
+        <is>
+          <t>紫竹讲坛\习读</t>
+        </is>
+      </c>
+      <c r="W13" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="X13" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="AA13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="AB13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">班会 </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -1149,6 +2070,76 @@
           <t>程子曦</t>
         </is>
       </c>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>18:00-19:00</t>
+        </is>
+      </c>
+      <c r="N14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语限时 </t>
+        </is>
+      </c>
+      <c r="O14" s="0" t="inlineStr">
+        <is>
+          <t>18:00-19:00</t>
+        </is>
+      </c>
+      <c r="P14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语限时 </t>
+        </is>
+      </c>
+      <c r="Q14" s="0" t="inlineStr">
+        <is>
+          <t>18:00-19:00</t>
+        </is>
+      </c>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物化限时 </t>
+        </is>
+      </c>
+      <c r="S14" s="0" t="inlineStr">
+        <is>
+          <t>18:00-19:00</t>
+        </is>
+      </c>
+      <c r="T14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文限时 </t>
+        </is>
+      </c>
+      <c r="U14" s="0" t="inlineStr">
+        <is>
+          <t>18:00-19:00</t>
+        </is>
+      </c>
+      <c r="V14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学限时 </t>
+        </is>
+      </c>
+      <c r="W14" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="X14" s="0" t="inlineStr">
+        <is>
+          <t>程子曦</t>
+        </is>
+      </c>
+      <c r="AA14" s="0" t="inlineStr">
+        <is>
+          <t>18:00-19:00</t>
+        </is>
+      </c>
+      <c r="AB14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语限时 </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -1201,6 +2192,76 @@
           <t>康立轩</t>
         </is>
       </c>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="N15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="O15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="P15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="Q15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="R15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="S15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="T15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="U15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="V15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="W15" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="X15" s="0" t="inlineStr">
+        <is>
+          <t>康立轩</t>
+        </is>
+      </c>
+      <c r="AA15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="AB15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -1253,6 +2314,76 @@
           <t>END</t>
         </is>
       </c>
+      <c r="M16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>陈1111浩</t>
+        </is>
+      </c>
+      <c r="O16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>陈1111浩</t>
+        </is>
+      </c>
+      <c r="Q16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="R16" s="0" t="inlineStr">
+        <is>
+          <t>倪宥霖</t>
+        </is>
+      </c>
+      <c r="S16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="T16" s="0" t="inlineStr">
+        <is>
+          <t>叶宇乐</t>
+        </is>
+      </c>
+      <c r="U16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="V16" s="0" t="inlineStr">
+        <is>
+          <t>孙丞怿</t>
+        </is>
+      </c>
+      <c r="W16" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="X16" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="AA16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>陈11浩</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
@@ -1295,6 +2426,66 @@
           <t>沈俊奕</t>
         </is>
       </c>
+      <c r="M17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="N17" s="0" t="inlineStr">
+        <is>
+          <t>黄思源</t>
+        </is>
+      </c>
+      <c r="O17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="P17" s="0" t="inlineStr">
+        <is>
+          <t>黄思源</t>
+        </is>
+      </c>
+      <c r="Q17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="R17" s="0" t="inlineStr">
+        <is>
+          <t>李玥呈</t>
+        </is>
+      </c>
+      <c r="S17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="T17" s="0" t="inlineStr">
+        <is>
+          <t>张一铭</t>
+        </is>
+      </c>
+      <c r="U17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="V17" s="0" t="inlineStr">
+        <is>
+          <t>沈俊奕</t>
+        </is>
+      </c>
+      <c r="AA17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="AB17" s="0" t="inlineStr">
+        <is>
+          <t>黄思源</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -1337,6 +2528,66 @@
           <t>END</t>
         </is>
       </c>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="N18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="O18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="P18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="Q18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="R18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="S18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="T18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="U18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="V18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="AA18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="AB18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
@@ -1355,7 +2606,7 @@
         </is>
       </c>
       <c r="B31" s="0" t="n">
-        <v>329</v>
+        <v>820</v>
       </c>
     </row>
     <row r="32">
@@ -1365,7 +2616,7 @@
         </is>
       </c>
       <c r="B32" s="0" t="n">
-        <v>629</v>
+        <v>640</v>
       </c>
     </row>
     <row r="33">
@@ -1387,7 +2638,7 @@
         </is>
       </c>
       <c r="B34" s="0" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
@@ -1397,11 +2648,31 @@
         </is>
       </c>
       <c r="B35" s="0" t="n">
-        <v>190</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>week_type</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>last_week_update</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:40:28</t>
+        </is>
+      </c>
+    </row>
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="B31" s="0" t="n">
-        <v>820</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="32">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="B32" s="0" t="n">
-        <v>640</v>
+        <v>830</v>
       </c>
     </row>
     <row r="33">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="B35" s="0" t="n">
-        <v>55</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="36">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>2026-01-11 21:40:28</t>
+          <t>2026-01-11 21:46:51</t>
         </is>
       </c>
     </row>
